--- a/Documents/Retrospective/overleg-27-Maart-2025.xlsx
+++ b/Documents/Retrospective/overleg-27-Maart-2025.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="96">
   <si>
     <t xml:space="preserve">A</t>
   </si>
@@ -162,15 +162,19 @@
     <t xml:space="preserve">Requirements en Specificaties</t>
   </si>
   <si>
-    <t xml:space="preserve">* Henk wil de Req&amp;Spec wel opschrijven. 
-* Github gebruiken om Change request in te dienen 
-* Ook Elly Jeroen erbij betrekken.</t>
+    <t xml:space="preserve">Henk wil de Req&amp;Spec wel opschrijven</t>
   </si>
   <si>
     <t xml:space="preserve">Specificaties opschrijven (ivm testen)</t>
   </si>
   <si>
+    <t xml:space="preserve">Github gebruiken om Change request in te dienen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Non-functional requirements maken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ook Elly Jeroen erbij betrekken.</t>
   </si>
   <si>
     <t xml:space="preserve">Meer gebruiken maken van wat er al is en goed functioneert. In Moode audio en Volumio zitten 10 jaar ontwikkeling. Waar we bijna niet van gebruik maken. Terwijl gelijkaardige features hebben. Dus, nog meer analyseren hoe het daar weer en dat gebruiken</t>
@@ -1252,48 +1256,58 @@
         <v>13</v>
       </c>
       <c r="D39" s="7"/>
-      <c r="E39" s="13"/>
+      <c r="E39" s="10" t="s">
+        <v>48</v>
+      </c>
       <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="G39" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="14" t="n">
         <v>3</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D40" s="15"/>
-      <c r="E40" s="13"/>
+      <c r="E40" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="G40" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
         <v>4</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="G41" s="8" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
         <v>5</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>11</v>
@@ -1308,14 +1322,14 @@
         <v>6</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
@@ -1325,14 +1339,14 @@
         <v>7</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C44" s="11" t="s">
         <v>11</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8" t="s">
@@ -1344,14 +1358,14 @@
         <v>8</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C45" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="8" t="s">
@@ -1363,7 +1377,7 @@
         <v>9</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>11</v>
@@ -1378,16 +1392,16 @@
         <v>10</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="s">
@@ -1399,14 +1413,14 @@
         <v>11</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D48" s="12"/>
-      <c r="E48" s="11" t="s">
-        <v>63</v>
+      <c r="E48" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8" t="s">
@@ -1418,13 +1432,13 @@
         <v>12</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="12"/>
-      <c r="E49" s="16"/>
+      <c r="E49" s="10"/>
       <c r="F49" s="8"/>
       <c r="G49" s="8"/>
     </row>
@@ -1433,7 +1447,7 @@
         <v>13</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>13</v>
@@ -1463,10 +1477,10 @@
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3" t="s">
@@ -1487,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>11</v>
@@ -1502,14 +1516,14 @@
         <v>2</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8" t="s">
@@ -1521,13 +1535,13 @@
         <v>3</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
@@ -1538,7 +1552,7 @@
         <v>4</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>13</v>
@@ -1553,7 +1567,7 @@
         <v>5</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>13</v>
@@ -1568,16 +1582,16 @@
         <v>6</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F59" s="8"/>
       <c r="G59" s="8" t="s">
@@ -1589,29 +1603,29 @@
         <v>9</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D60" s="12"/>
-      <c r="E60" s="11"/>
+      <c r="E60" s="8"/>
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
     </row>
-    <row r="61" customFormat="false" ht="24.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="n">
         <v>7</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D61" s="12"/>
-      <c r="E61" s="16" t="s">
-        <v>80</v>
+      <c r="E61" s="10" t="s">
+        <v>82</v>
       </c>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
@@ -1622,24 +1636,24 @@
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="0"/>
       <c r="B63" s="0" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="0"/>
       <c r="B64" s="0" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="0"/>
       <c r="B65" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1664,13 +1678,12 @@
       <c r="B73" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="D38:D39"/>
-    <mergeCell ref="E38:E40"/>
     <mergeCell ref="D47:D49"/>
     <mergeCell ref="D56:D58"/>
     <mergeCell ref="D59:D61"/>
@@ -1729,47 +1742,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B2" s="8"/>
     </row>
     <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="21" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B7" s="8"/>
     </row>
